--- a/heart_noisy.xlsx
+++ b/heart_noisy.xlsx
@@ -1,23 +1,25 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\shukl\Documents\GitHub\heart\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38007F7B-7484-41D8-9266-E30FF01527DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E05D0A3-24BC-4F73-819A-1E3C483AEA44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{17EA2864-75EB-4856-BEA7-292655FA3F25}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="3" xr2:uid="{17EA2864-75EB-4856-BEA7-292655FA3F25}"/>
   </bookViews>
   <sheets>
-    <sheet name="DT_0%_rank13" sheetId="1" r:id="rId1"/>
-    <sheet name="DT_10%_rank13" sheetId="3" r:id="rId2"/>
-    <sheet name="DT_20%_rank13" sheetId="4" r:id="rId3"/>
+    <sheet name="DT_10%_rank13" sheetId="3" r:id="rId1"/>
+    <sheet name="DT_20%_rank13" sheetId="4" r:id="rId2"/>
+    <sheet name="SVM_10%_rank13" sheetId="5" r:id="rId3"/>
+    <sheet name="SVM_20%_rank13" sheetId="1" r:id="rId4"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="27">
   <si>
     <t>PREDICTED</t>
   </si>
@@ -55,8 +57,155 @@
     <t>highchance</t>
   </si>
   <si>
+    <t>no scaling</t>
+  </si>
+  <si>
+    <t>DT on raw data</t>
+  </si>
+  <si>
+    <t>DT on Curated Data</t>
+  </si>
+  <si>
+    <r>
+      <t>max_attributes =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF098156"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>5</t>
+    </r>
+  </si>
+  <si>
     <r>
       <t>max_depth=depth,random_state=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF098156"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>22</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>,criterion=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>"gini"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t xml:space="preserve">,min_samples_split = </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF098156"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>10</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>max_attributes =</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF795E26"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>len</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF257693"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>list</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>(df_test))</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF098156"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>-1</t>
+    </r>
+  </si>
+  <si>
+    <t>SVM on raw data</t>
+  </si>
+  <si>
+    <t>SVM on Curated Data</t>
+  </si>
+  <si>
+    <r>
+      <t>classifier =svm.SVC(kernel=</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FFA31515"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>"rbf"</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
+        <color rgb="FF000000"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>, gamma=</t>
     </r>
     <r>
       <rPr>
@@ -65,7 +214,7 @@
         <rFont val="Courier New"/>
         <family val="3"/>
       </rPr>
-      <t>22</t>
+      <t>0.01</t>
     </r>
     <r>
       <rPr>
@@ -74,16 +223,16 @@
         <rFont val="Courier New"/>
         <family val="3"/>
       </rPr>
-      <t>,criterion=</t>
+      <t xml:space="preserve"> ,C=</t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>"gini"</t>
+        <color rgb="FF098156"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>0.9</t>
     </r>
     <r>
       <rPr>
@@ -92,7 +241,7 @@
         <rFont val="Courier New"/>
         <family val="3"/>
       </rPr>
-      <t xml:space="preserve">,min_samples_split = </t>
+      <t xml:space="preserve"> ,random_state=</t>
     </r>
     <r>
       <rPr>
@@ -101,21 +250,7 @@
         <rFont val="Courier New"/>
         <family val="3"/>
       </rPr>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">max_attributes = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="8"/>
-        <color rgb="FF795E26"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>len</t>
+      <t>22</t>
     </r>
     <r>
       <rPr>
@@ -124,16 +259,24 @@
         <rFont val="Courier New"/>
         <family val="3"/>
       </rPr>
-      <t>(</t>
+      <t>)</t>
+    </r>
+  </si>
+  <si>
+    <t>cv=15</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">        </t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <color rgb="FF257693"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>list</t>
+        <color rgb="FFAF00DB"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>from</t>
     </r>
     <r>
       <rPr>
@@ -142,147 +285,66 @@
         <rFont val="Courier New"/>
         <family val="3"/>
       </rPr>
-      <t>(df_test))</t>
+      <t xml:space="preserve"> sklearn.preprocessing </t>
     </r>
     <r>
       <rPr>
         <sz val="8"/>
-        <color rgb="FF098156"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>-1</t>
-    </r>
-  </si>
-  <si>
-    <t>no scaling</t>
-  </si>
-  <si>
-    <t>DT on raw data</t>
-  </si>
-  <si>
-    <t>DT on Curated Data</t>
-  </si>
-  <si>
-    <r>
-      <t>max_attributes =</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF098156"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>5</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>max_depth=depth,random_state=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF098156"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>22</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+        <color rgb="FFAF00DB"/>
+        <rFont val="Courier New"/>
+        <family val="3"/>
+      </rPr>
+      <t>import</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="8"/>
         <color rgb="FF000000"/>
         <rFont val="Courier New"/>
         <family val="3"/>
       </rPr>
-      <t>,criterion=</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FFA31515"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>"gini"</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t xml:space="preserve">,min_samples_split = </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF098156"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>10</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>max_attributes =</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF795E26"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>len</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF257693"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>list</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>(df_test))</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF098156"/>
-        <rFont val="Courier New"/>
-        <family val="3"/>
-      </rPr>
-      <t>-1</t>
-    </r>
+      <t xml:space="preserve"> scale</t>
+    </r>
+  </si>
+  <si>
+    <t>        x_train = scale(x_train)</t>
+  </si>
+  <si>
+    <t>        x_test=scale(x_test)</t>
+  </si>
+  <si>
+    <t>        grid.fit(x_train, y_train)</t>
+  </si>
+  <si>
+    <t>        param=grid.best_params_</t>
+  </si>
+  <si>
+    <t>        from sklearn.model_selection import GridSearchCV</t>
+  </si>
+  <si>
+    <t>        param_grid = {'C': [100], 'gamma': [0.0001,0.00001,0.001,.01,0.1],'kernel':['rbf']}</t>
+  </si>
+  <si>
+    <t>        grid = GridSearchCV(SVC(), param_grid, refit = True, verbose = 0)</t>
+  </si>
+  <si>
+    <t>        C_best=param['C']</t>
+  </si>
+  <si>
+    <t>        gamma_best=param['gamma']</t>
+  </si>
+  <si>
+    <t>        kernel_best=param['kernel']</t>
+  </si>
+  <si>
+    <t>        classifier =svm.SVC(gamma=gamma_best, kernel=kernel_best,C=C_best, random_state=22)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -307,30 +369,6 @@
     <font>
       <sz val="8"/>
       <color rgb="FF000000"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF098156"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FFA31515"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF795E26"/>
-      <name val="Courier New"/>
-      <family val="3"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <color rgb="FF257693"/>
       <name val="Courier New"/>
       <family val="3"/>
     </font>
@@ -364,6 +402,24 @@
       <name val="Courier New"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFA31515"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FF098156"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <color rgb="FFAF00DB"/>
+      <name val="Courier New"/>
+      <family val="3"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -599,6 +655,9 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -634,9 +693,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -951,41 +1007,42 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA328F72-955F-4815-9356-B8C9EF3B1194}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB465A6-31FF-4F12-A408-F9D0D272FDE3}">
+  <dimension ref="A1:F17"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.85546875" customWidth="1"/>
-    <col min="4" max="5" width="12.42578125" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12" customWidth="1"/>
+    <col min="4" max="4" width="11.44140625" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" customWidth="1"/>
+    <col min="6" max="6" width="11.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="18"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="19" t="s">
+      <c r="D2" s="21"/>
+      <c r="E2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1001,36 +1058,36 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="b">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="b">
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="6">
-        <v>0.72182299999999999</v>
+        <v>0.68345299999999998</v>
       </c>
       <c r="D4" s="7">
-        <v>0.27817700000000001</v>
+        <v>0.31654700000000002</v>
       </c>
       <c r="E4" s="6">
-        <v>0.72661900000000001</v>
+        <v>0.69544399999999995</v>
       </c>
       <c r="F4" s="7">
-        <v>0.27338099999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
+        <v>0.30455599999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="23"/>
       <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="9">
-        <v>0.162272</v>
+        <v>0.17038500000000001</v>
       </c>
       <c r="D5" s="10">
-        <v>0.83772800000000003</v>
+        <v>0.82961499999999999</v>
       </c>
       <c r="E5" s="9">
         <v>0.1643</v>
@@ -1039,66 +1096,54 @@
         <v>0.8357</v>
       </c>
     </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="15">
-        <v>0.83772800000000003</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="15">
+      <c r="B7" s="25"/>
+      <c r="C7" s="16">
+        <v>0.82961499999999999</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="16">
         <v>0.8357</v>
       </c>
-      <c r="F7" s="16"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15">
-        <v>0.27817700000000001</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15">
-        <v>0.27338099999999999</v>
-      </c>
-      <c r="F8" s="16"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C13" s="12" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="16">
+        <v>0.31654700000000002</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16">
+        <v>0.30455599999999999</v>
+      </c>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="13" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="12" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C20" s="12"/>
-    </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C21" s="12"/>
-    </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C22" s="12"/>
-    </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C23" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1120,42 +1165,41 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABB465A6-31FF-4F12-A408-F9D0D272FDE3}">
-  <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83691AC4-3296-4229-9252-61507CFC5488}">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="11.42578125" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" customWidth="1"/>
-    <col min="6" max="6" width="11.28515625" customWidth="1"/>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.33203125" customWidth="1"/>
+    <col min="5" max="6" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="18"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="18" t="s">
+        <v>6</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="18" t="s">
+        <v>7</v>
+      </c>
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="19" t="s">
+      <c r="D2" s="21"/>
+      <c r="E2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1171,92 +1215,104 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="b">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="b">
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="6">
-        <v>0.68345299999999998</v>
+        <v>0.68585099999999999</v>
       </c>
       <c r="D4" s="7">
-        <v>0.31654700000000002</v>
+        <v>0.31414900000000001</v>
       </c>
       <c r="E4" s="6">
-        <v>0.69544399999999995</v>
+        <v>0.71223000000000003</v>
       </c>
       <c r="F4" s="7">
-        <v>0.30455599999999999</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
+        <v>0.28777000000000003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="23"/>
       <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="9">
-        <v>0.17038500000000001</v>
+        <v>0.186613</v>
       </c>
       <c r="D5" s="10">
-        <v>0.82961499999999999</v>
+        <v>0.81338699999999997</v>
       </c>
       <c r="E5" s="9">
-        <v>0.1643</v>
+        <v>0.19472600000000001</v>
       </c>
       <c r="F5" s="10">
-        <v>0.8357</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.80527400000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
     </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="15">
-        <v>0.82961499999999999</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="15">
-        <v>0.8357</v>
-      </c>
-      <c r="F7" s="16"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="16">
+        <v>0.81338699999999997</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="16">
+        <v>0.80527400000000005</v>
+      </c>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15">
-        <v>0.31654700000000002</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15">
-        <v>0.30455599999999999</v>
-      </c>
-      <c r="F8" s="16"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C13" s="25" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="25" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="16">
+        <v>0.31414900000000001</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16">
+        <v>0.28777000000000003</v>
+      </c>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="13" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="13" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>7</v>
-      </c>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C20" s="12"/>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C21" s="12"/>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C22" s="12"/>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C23" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="11">
@@ -1278,41 +1334,57 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83691AC4-3296-4229-9252-61507CFC5488}">
-  <dimension ref="A1:F23"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1B10688D-6378-410E-8D05-7C681B24B4DF}">
+  <dimension ref="A1:P26"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="9.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.7109375" customWidth="1"/>
-    <col min="4" max="4" width="10.28515625" customWidth="1"/>
-    <col min="5" max="6" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="10.44140625" customWidth="1"/>
+    <col min="4" max="4" width="10.77734375" customWidth="1"/>
+    <col min="5" max="5" width="10.5546875" customWidth="1"/>
+    <col min="6" max="6" width="11.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1"/>
       <c r="B1" s="1"/>
-      <c r="C1" s="17" t="s">
-        <v>8</v>
-      </c>
-      <c r="D1" s="18"/>
-      <c r="E1" s="17" t="s">
-        <v>9</v>
-      </c>
-      <c r="F1" s="18"/>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C1" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D1" s="19"/>
+      <c r="E1" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F1" s="19"/>
+      <c r="M1" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="N1" s="19"/>
+      <c r="O1" s="18" t="s">
+        <v>12</v>
+      </c>
+      <c r="P1" s="19"/>
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" s="2"/>
       <c r="B2" s="2"/>
-      <c r="C2" s="19" t="s">
+      <c r="C2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="20"/>
-      <c r="E2" s="19" t="s">
+      <c r="D2" s="21"/>
+      <c r="E2" s="20" t="s">
         <v>0</v>
       </c>
-      <c r="F2" s="20"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="F2" s="21"/>
+      <c r="M2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="N2" s="21"/>
+      <c r="O2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="P2" s="21"/>
+    </row>
+    <row r="3" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="2"/>
       <c r="B3" s="2"/>
       <c r="C3" s="3" t="s">
@@ -1327,105 +1399,427 @@
       <c r="F3" s="4" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="21" t="b">
+      <c r="M3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="N3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="b">
         <v>1</v>
       </c>
       <c r="B4" s="5" t="s">
         <v>3</v>
       </c>
       <c r="C4" s="6">
-        <v>0.68585099999999999</v>
+        <v>0.60431699999999999</v>
       </c>
       <c r="D4" s="7">
-        <v>0.31414900000000001</v>
+        <v>0.39568300000000001</v>
       </c>
       <c r="E4" s="6">
-        <v>0.71223000000000003</v>
+        <v>0.59712200000000004</v>
       </c>
       <c r="F4" s="7">
-        <v>0.28777000000000003</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="22"/>
+        <v>0.40287800000000001</v>
+      </c>
+      <c r="M4" s="6">
+        <v>0.705036</v>
+      </c>
+      <c r="N4" s="7">
+        <v>0.294964</v>
+      </c>
+      <c r="O4" s="6">
+        <v>0.70743400000000001</v>
+      </c>
+      <c r="P4" s="7">
+        <v>0.29256599999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="23"/>
       <c r="B5" s="8" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="9">
-        <v>0.186613</v>
+        <v>0.19269800000000001</v>
       </c>
       <c r="D5" s="10">
-        <v>0.81338699999999997</v>
+        <v>0.80730199999999996</v>
       </c>
       <c r="E5" s="9">
-        <v>0.19472600000000001</v>
+        <v>0.15415799999999999</v>
       </c>
       <c r="F5" s="10">
-        <v>0.80527400000000005</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+        <v>0.84584199999999998</v>
+      </c>
+      <c r="M5" s="9">
+        <v>8.9248999999999995E-2</v>
+      </c>
+      <c r="N5" s="10">
+        <v>0.91075099999999998</v>
+      </c>
+      <c r="O5" s="9">
+        <v>6.8966E-2</v>
+      </c>
+      <c r="P5" s="10">
+        <v>0.93103400000000003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C6" s="11"/>
       <c r="D6" s="11"/>
       <c r="E6" s="11"/>
       <c r="F6" s="11"/>
-    </row>
-    <row r="7" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="23" t="s">
+      <c r="M6" s="11"/>
+      <c r="N6" s="11"/>
+      <c r="O6" s="11"/>
+      <c r="P6" s="11"/>
+    </row>
+    <row r="7" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="B7" s="24"/>
-      <c r="C7" s="15">
-        <v>0.81338699999999997</v>
-      </c>
-      <c r="D7" s="16"/>
-      <c r="E7" s="15">
-        <v>0.80527400000000005</v>
-      </c>
-      <c r="F7" s="16"/>
-    </row>
-    <row r="8" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="13" t="s">
+      <c r="B7" s="25"/>
+      <c r="C7" s="16">
+        <v>0.80730199999999996</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="16">
+        <v>0.84584199999999998</v>
+      </c>
+      <c r="F7" s="17"/>
+      <c r="M7" s="16">
+        <v>0.91075099999999998</v>
+      </c>
+      <c r="N7" s="17"/>
+      <c r="O7" s="16">
+        <v>0.93103400000000003</v>
+      </c>
+      <c r="P7" s="17"/>
+    </row>
+    <row r="8" spans="1:16" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="B8" s="14"/>
-      <c r="C8" s="15">
-        <v>0.31414900000000001</v>
-      </c>
-      <c r="D8" s="16"/>
-      <c r="E8" s="15">
-        <v>0.28777000000000003</v>
-      </c>
-      <c r="F8" s="16"/>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C13" s="25" t="s">
+      <c r="B8" s="15"/>
+      <c r="C8" s="16">
+        <v>0.39568300000000001</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16">
+        <v>0.40287800000000001</v>
+      </c>
+      <c r="F8" s="17"/>
+      <c r="M8" s="16">
+        <v>0.294964</v>
+      </c>
+      <c r="N8" s="17"/>
+      <c r="O8" s="16">
+        <v>0.29256599999999999</v>
+      </c>
+      <c r="P8" s="17"/>
+    </row>
+    <row r="10" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M10" s="12" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C11" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="13" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C13" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C14" s="13" t="s">
+        <v>22</v>
+      </c>
+      <c r="M14" s="12" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="15" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="M15" s="12" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="C16" s="12" t="s">
+        <v>18</v>
+      </c>
+      <c r="M16" s="12" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C17" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C20" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C21" s="12"/>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C22" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C23" s="12"/>
+    </row>
+    <row r="24" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C24" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="26" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C26" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="19">
+    <mergeCell ref="M8:N8"/>
+    <mergeCell ref="O8:P8"/>
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="M7:N7"/>
+    <mergeCell ref="O7:P7"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="E8:F8"/>
+    <mergeCell ref="C1:D1"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="C2:D2"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="A7:B7"/>
+    <mergeCell ref="C7:D7"/>
+    <mergeCell ref="E7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DA328F72-955F-4815-9356-B8C9EF3B1194}">
+  <dimension ref="A1:F25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="2" max="2" width="9.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.88671875" customWidth="1"/>
+    <col min="4" max="5" width="12.44140625" customWidth="1"/>
+    <col min="6" max="6" width="13.6640625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1"/>
+      <c r="C1" s="18" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="25" t="s">
+      <c r="D1" s="19"/>
+      <c r="E1" s="18" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="17" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="F1" s="19"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2"/>
+      <c r="B2" s="2"/>
+      <c r="C2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="D2" s="21"/>
+      <c r="E2" s="20" t="s">
+        <v>0</v>
+      </c>
+      <c r="F2" s="21"/>
+    </row>
+    <row r="3" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="2"/>
+      <c r="B3" s="2"/>
+      <c r="C3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="22" t="b">
+        <v>1</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C4" s="6">
+        <v>0.57793799999999995</v>
+      </c>
+      <c r="D4" s="7">
+        <v>0.42206199999999999</v>
+      </c>
+      <c r="E4" s="6">
+        <v>0.58513199999999999</v>
+      </c>
+      <c r="F4" s="7">
+        <v>0.41486800000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="23"/>
+      <c r="B5" s="8" t="s">
+        <v>4</v>
+      </c>
+      <c r="C5" s="9">
+        <v>0.19878299999999999</v>
+      </c>
+      <c r="D5" s="10">
+        <v>0.80121699999999996</v>
+      </c>
+      <c r="E5" s="9">
+        <v>0.166329</v>
+      </c>
+      <c r="F5" s="10">
+        <v>0.83367100000000005</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C6" s="11"/>
+      <c r="D6" s="11"/>
+      <c r="E6" s="11"/>
+      <c r="F6" s="11"/>
+    </row>
+    <row r="7" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" s="25"/>
+      <c r="C7" s="16">
+        <v>0.80121699999999996</v>
+      </c>
+      <c r="D7" s="17"/>
+      <c r="E7" s="16">
+        <v>0.83367100000000005</v>
+      </c>
+      <c r="F7" s="17"/>
+    </row>
+    <row r="8" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="14" t="s">
+        <v>2</v>
+      </c>
+      <c r="B8" s="15"/>
+      <c r="C8" s="16">
+        <v>0.42206199999999999</v>
+      </c>
+      <c r="D8" s="17"/>
+      <c r="E8" s="16">
+        <v>0.41486800000000001</v>
+      </c>
+      <c r="F8" s="17"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C10" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C12" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C13" s="13" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="12" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C16" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C17" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="3:3" x14ac:dyDescent="0.25">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="18" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C19" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C20" s="12"/>
     </row>
-    <row r="21" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C21" s="12"/>
-    </row>
-    <row r="22" spans="3:3" x14ac:dyDescent="0.25">
+    <row r="21" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C21" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="22" spans="3:3" x14ac:dyDescent="0.3">
       <c r="C22" s="12"/>
     </row>
-    <row r="23" spans="3:3" x14ac:dyDescent="0.25">
-      <c r="C23" s="12"/>
+    <row r="23" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C23" s="12" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="25" spans="3:3" x14ac:dyDescent="0.3">
+      <c r="C25" t="s">
+        <v>14</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="11">
